--- a/doc/jdt.xlsx
+++ b/doc/jdt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game_de_la_fin_danne\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pa22yog\Documents\GitHub\Shoot-em-up-i320\Shoot-em-UP-game\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C85F2A-545E-4F31-A984-B31DF849111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D1097A-D7C7-420C-8BEE-87E8BD330840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="18" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Apprenti.e</t>
   </si>
@@ -106,88 +106,16 @@
     <t>Total en heures</t>
   </si>
   <si>
-    <t>Installation du logiciel, configuration de Git</t>
+    <t>Introduction dans le projet</t>
   </si>
   <si>
-    <t>répartition des groupes, élaboration de projets</t>
+    <t>Créeation de repos Git, travail avec CDC</t>
   </si>
   <si>
-    <t>travail sur cdc</t>
+    <t xml:space="preserve">Création du concept de joue </t>
   </si>
   <si>
-    <t>Concevoir le système de déplacement du joueur et rotations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concevoir des animations pour le personnage </t>
-  </si>
-  <si>
-    <t>Amélioration du script de movement</t>
-  </si>
-  <si>
-    <t>Concevoir le système d’interaction avec les objets </t>
-  </si>
-  <si>
-    <t>Concevoir le système de caméra </t>
-  </si>
-  <si>
-    <t>J'ai créé un système permettant d'afficher des énigmes à l'écran</t>
-  </si>
-  <si>
-    <t>J'ai ajouté les énigmes sur la carte, avec leurs descriptions, un minuteur et des indices d'interaction à l'écran.</t>
-  </si>
-  <si>
-    <t>Projet personnel</t>
-  </si>
-  <si>
-    <t>Conception du système de caméra. Modification des scènes de la chambre et du couloir.</t>
-  </si>
-  <si>
-    <t>Amélioration de l'interface utilisateur.</t>
-  </si>
-  <si>
-    <t>Modification du système d'éclairage et ajout du changement de scène.</t>
-  </si>
-  <si>
-    <t>Modification de la scène de la chambre du docteur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise à jour de la version du moteur de jeu. Modification de la salle du doctor. </t>
-  </si>
-  <si>
-    <t>Verrouillage de la position du dialogue au bon endroit</t>
-  </si>
-  <si>
-    <t>Sauvegarde de l'index de la position de la caméra</t>
-  </si>
-  <si>
-    <t>Ajout de la possibilité de passer les dialogues et intégration du bouton de skip</t>
-  </si>
-  <si>
-    <t>Concevoir le système des énigmes et l'integration dans le jeu</t>
-  </si>
-  <si>
-    <t>création d'un scénario pour le jeu</t>
-  </si>
-  <si>
-    <t>apprentissage de JavaScript par la lecture "eloquent javascript"</t>
-  </si>
-  <si>
-    <t>CDC</t>
-  </si>
-  <si>
-    <t>Git</t>
-  </si>
-  <si>
-    <t>Git/movement</t>
-  </si>
-  <si>
-    <t>Git/camera</t>
-  </si>
-  <si>
-    <t>Git/enigmes</t>
-  </si>
-  <si>
-    <t>Eloquent JavaScript</t>
+    <t>Création de prémier User Story</t>
   </si>
 </sst>
 </file>
@@ -425,7 +353,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -536,6 +464,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -600,40 +541,33 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -951,25 +885,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E240"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="14.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="103" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="1"/>
+    <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
+      <c r="C1" s="36"/>
       <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
@@ -981,10 +915,10 @@
       <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="21" t="s">
         <v>6</v>
       </c>
@@ -996,8 +930,8 @@
       <c r="A3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="21" t="s">
         <v>9</v>
       </c>
@@ -1007,10 +941,10 @@
       <c r="A4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -1031,115 +965,97 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="39">
-        <v>46174</v>
+      <c r="B6" s="43">
+        <v>46262</v>
       </c>
       <c r="C6" s="5">
-        <v>90</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="40"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="8">
-        <v>90</v>
-      </c>
-      <c r="D7" s="52"/>
+        <v>20</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>19</v>
+      </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="40"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="8">
-        <v>90</v>
-      </c>
-      <c r="D8" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="50" t="s">
-        <v>40</v>
-      </c>
+      <c r="E8" s="57"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="40"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="8">
-        <v>90</v>
-      </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="51"/>
+        <v>30</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="56"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
-      <c r="B10" s="41"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="39">
-        <v>46175</v>
-      </c>
-      <c r="C12" s="5">
-        <v>90</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>41</v>
-      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="54"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="8">
-        <v>90</v>
-      </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="51"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="56"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="8">
-        <v>90</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>42</v>
-      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="57"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="8">
-        <v>90</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="51"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="56"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="41"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="10"/>
@@ -1148,62 +1064,42 @@
       <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="39">
-        <v>46177</v>
-      </c>
-      <c r="C18" s="5">
-        <v>90</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="56" t="s">
-        <v>42</v>
-      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="33"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="8">
-        <v>90</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>24</v>
-      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="8">
-        <v>90</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>43</v>
-      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="57"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="8">
-        <v>90</v>
-      </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="51"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="56"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
-      <c r="B22" s="41"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
       <c r="E22" s="10"/>
@@ -1212,56 +1108,42 @@
       <c r="A23" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="42"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="39">
-        <v>46178</v>
-      </c>
-      <c r="C24" s="5">
-        <v>90</v>
-      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="5"/>
       <c r="D24"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="8">
-        <v>90</v>
-      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="8">
-        <v>90</v>
-      </c>
-      <c r="D26" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="B26" s="44"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="57"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="8">
-        <v>90</v>
-      </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="51"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="56"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
-      <c r="B28" s="41"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
       <c r="E28" s="10"/>
@@ -1270,56 +1152,42 @@
       <c r="A29" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="38"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
-      <c r="B30" s="39">
-        <v>46184</v>
-      </c>
-      <c r="C30" s="5">
-        <v>90</v>
-      </c>
-      <c r="D30" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="55" t="s">
-        <v>44</v>
-      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="54"/>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="8">
-        <v>90</v>
-      </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="59"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="55"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="8">
-        <v>90</v>
-      </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="59"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="55"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="8">
-        <v>90</v>
-      </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="51"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="56"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
-      <c r="B34" s="41"/>
+      <c r="B34" s="45"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -1328,124 +1196,86 @@
       <c r="A35" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="38"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="42"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="39">
-        <v>46185</v>
-      </c>
-      <c r="C36" s="5">
-        <v>90</v>
-      </c>
+      <c r="B36" s="43"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="8">
-        <v>90</v>
-      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="8"/>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="8">
-        <v>90</v>
-      </c>
-      <c r="D38" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="50" t="s">
-        <v>44</v>
-      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="57"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="8">
-        <v>45</v>
-      </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="51"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="56"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="10">
-        <v>45</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>28</v>
-      </c>
+      <c r="B40" s="45"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="38"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="39">
-        <v>46190</v>
-      </c>
-      <c r="C42" s="5">
-        <v>90</v>
-      </c>
-      <c r="D42" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="55" t="s">
-        <v>41</v>
-      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="5"/>
+      <c r="D42"/>
+      <c r="E42" s="54"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="8">
-        <v>90</v>
-      </c>
-      <c r="D43" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="59"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="8"/>
+      <c r="D43"/>
+      <c r="E43" s="55"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="8">
-        <v>90</v>
-      </c>
-      <c r="D44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="59"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="8"/>
+      <c r="D44"/>
+      <c r="E44" s="55"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="8">
-        <v>90</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="51"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="8"/>
+      <c r="D45"/>
+      <c r="E45" s="56"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="41"/>
+      <c r="B46" s="45"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11"/>
       <c r="E46" s="10"/>
@@ -1454,62 +1284,42 @@
       <c r="A47" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="38"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="42"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="39">
-        <v>46191</v>
-      </c>
-      <c r="C48" s="5">
-        <v>90</v>
-      </c>
-      <c r="D48" t="s">
-        <v>33</v>
-      </c>
-      <c r="E48" s="55" t="s">
-        <v>41</v>
-      </c>
+      <c r="B48" s="43"/>
+      <c r="C48" s="5"/>
+      <c r="D48"/>
+      <c r="E48" s="54"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="8">
-        <v>90</v>
-      </c>
-      <c r="D49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E49" s="59"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="8"/>
+      <c r="D49"/>
+      <c r="E49" s="55"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="8">
-        <v>90</v>
-      </c>
-      <c r="D50" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="59"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="8"/>
+      <c r="D50"/>
+      <c r="E50" s="55"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="8">
-        <v>90</v>
-      </c>
-      <c r="D51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="51"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="8"/>
+      <c r="D51"/>
+      <c r="E51" s="56"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
-      <c r="B52" s="41"/>
+      <c r="B52" s="45"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="10"/>
@@ -1518,60 +1328,42 @@
       <c r="A53" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B53" s="36"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="42"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="39">
-        <v>46192</v>
-      </c>
-      <c r="C54" s="5">
-        <v>90</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
+      <c r="A54" s="13"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="5"/>
+      <c r="D54"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="8">
-        <v>90</v>
-      </c>
-      <c r="D55" t="s">
-        <v>38</v>
-      </c>
+      <c r="A55" s="8"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="8"/>
+      <c r="D55"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="8">
-        <v>90</v>
-      </c>
-      <c r="D56" t="s">
-        <v>38</v>
-      </c>
+      <c r="A56" s="8"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="8"/>
+      <c r="D56"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="8">
-        <v>90</v>
-      </c>
-      <c r="D57" t="s">
-        <v>38</v>
-      </c>
+      <c r="A57" s="8"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="8"/>
+      <c r="D57"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10"/>
-      <c r="B58" s="41"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="45"/>
       <c r="C58" s="10"/>
       <c r="D58" s="11"/>
       <c r="E58" s="10"/>
@@ -1580,62 +1372,42 @@
       <c r="A59" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B59" s="36"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="38"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="42"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
-      <c r="B60" s="39">
-        <v>46195</v>
-      </c>
-      <c r="C60" s="5">
-        <v>90</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="55" t="s">
-        <v>45</v>
-      </c>
+      <c r="B60" s="43"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="54"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="8">
-        <v>90</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E61" s="59"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="55"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
-      <c r="B62" s="40"/>
-      <c r="C62" s="8">
-        <v>90</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62" s="59"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="55"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="8">
-        <v>90</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E63" s="51"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="56"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
-      <c r="B64" s="41"/>
+      <c r="B64" s="45"/>
       <c r="C64" s="10"/>
       <c r="D64" s="11"/>
       <c r="E64" s="10"/>
@@ -1644,63 +1416,47 @@
       <c r="A65" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="36"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="38"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="42"/>
     </row>
     <row r="66" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="39">
-        <v>46196</v>
-      </c>
-      <c r="C66" s="5">
-        <v>90</v>
-      </c>
+      <c r="A66" s="4"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="5"/>
       <c r="D66" s="14"/>
-      <c r="E66" s="55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="8">
-        <v>90</v>
-      </c>
+      <c r="E66" s="54"/>
+    </row>
+    <row r="67" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="7"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="8"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="59"/>
-    </row>
-    <row r="68" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="8">
-        <v>90</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68" s="59"/>
+      <c r="E67" s="55"/>
+    </row>
+    <row r="68" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="7"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="55"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="8"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="8">
-        <v>90</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E69" s="51"/>
-    </row>
-    <row r="70" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="41"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="56"/>
+    </row>
+    <row r="70" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="45"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
     </row>
-    <row r="71" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>16</v>
       </c>
@@ -1711,7 +1467,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
-      <c r="B72" s="44"/>
+      <c r="B72" s="48"/>
       <c r="C72" s="5">
         <v>90</v>
       </c>
@@ -1720,7 +1476,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
-      <c r="B73" s="40"/>
+      <c r="B73" s="44"/>
       <c r="C73" s="8">
         <v>90</v>
       </c>
@@ -1729,7 +1485,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
-      <c r="B74" s="40"/>
+      <c r="B74" s="44"/>
       <c r="C74" s="8">
         <v>90</v>
       </c>
@@ -1738,32 +1494,32 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
-      <c r="B75" s="40"/>
+      <c r="B75" s="44"/>
       <c r="C75" s="8">
         <v>90</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
     </row>
-    <row r="76" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
-      <c r="B76" s="41"/>
+      <c r="B76" s="45"/>
       <c r="C76" s="10"/>
       <c r="D76" s="11"/>
       <c r="E76" s="10"/>
     </row>
-    <row r="77" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="36"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="38"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="42"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="B78" s="44"/>
+      <c r="A78" s="13"/>
+      <c r="B78" s="48"/>
       <c r="C78" s="5">
         <v>90</v>
       </c>
@@ -1771,8 +1527,8 @@
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="7"/>
-      <c r="B79" s="40"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="44"/>
       <c r="C79" s="8">
         <v>90</v>
       </c>
@@ -1780,8 +1536,8 @@
       <c r="E79" s="8"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="7"/>
-      <c r="B80" s="40"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="44"/>
       <c r="C80" s="8">
         <v>90</v>
       </c>
@@ -1789,33 +1545,33 @@
       <c r="E80" s="8"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="7"/>
-      <c r="B81" s="40"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="44"/>
       <c r="C81" s="8">
         <v>90</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
     </row>
-    <row r="82" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="10"/>
-      <c r="B82" s="41"/>
+    <row r="82" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="45"/>
       <c r="C82" s="10"/>
       <c r="D82" s="11"/>
       <c r="E82" s="10"/>
     </row>
-    <row r="83" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B83" s="36"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="38"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="42"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
-      <c r="B84" s="44"/>
+      <c r="B84" s="48"/>
       <c r="C84" s="5">
         <v>90</v>
       </c>
@@ -1824,7 +1580,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
-      <c r="B85" s="40"/>
+      <c r="B85" s="44"/>
       <c r="C85" s="8">
         <v>90</v>
       </c>
@@ -1833,7 +1589,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
-      <c r="B86" s="40"/>
+      <c r="B86" s="44"/>
       <c r="C86" s="8">
         <v>90</v>
       </c>
@@ -1842,28 +1598,28 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
-      <c r="B87" s="40"/>
+      <c r="B87" s="44"/>
       <c r="C87" s="8">
         <v>90</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="8"/>
     </row>
-    <row r="88" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
-      <c r="B88" s="41"/>
+      <c r="B88" s="45"/>
       <c r="C88" s="10"/>
       <c r="D88" s="11"/>
       <c r="E88" s="10"/>
     </row>
-    <row r="89" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B89" s="36"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="38"/>
+      <c r="B89" s="40"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="42"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
@@ -1901,14 +1657,14 @@
       <c r="D93" s="31"/>
       <c r="E93" s="8"/>
     </row>
-    <row r="94" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="23"/>
       <c r="C94" s="8"/>
       <c r="D94" s="9"/>
       <c r="E94" s="8"/>
     </row>
-    <row r="95" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>16</v>
       </c>
@@ -1919,7 +1675,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
-      <c r="B96" s="44"/>
+      <c r="B96" s="48"/>
       <c r="C96" s="5">
         <v>90</v>
       </c>
@@ -1928,7 +1684,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
-      <c r="B97" s="40"/>
+      <c r="B97" s="44"/>
       <c r="C97" s="8">
         <v>90</v>
       </c>
@@ -1937,7 +1693,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
-      <c r="B98" s="40"/>
+      <c r="B98" s="44"/>
       <c r="C98" s="8">
         <v>90</v>
       </c>
@@ -1946,32 +1702,32 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7"/>
-      <c r="B99" s="40"/>
+      <c r="B99" s="44"/>
       <c r="C99" s="8">
         <v>90</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="8"/>
     </row>
-    <row r="100" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
-      <c r="B100" s="41"/>
+      <c r="B100" s="45"/>
       <c r="C100" s="10"/>
       <c r="D100" s="11"/>
       <c r="E100" s="10"/>
     </row>
-    <row r="101" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="38"/>
+      <c r="B101" s="40"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="42"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="4"/>
-      <c r="B102" s="44"/>
+      <c r="B102" s="48"/>
       <c r="C102" s="5">
         <v>90</v>
       </c>
@@ -1980,7 +1736,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7"/>
-      <c r="B103" s="40"/>
+      <c r="B103" s="44"/>
       <c r="C103" s="8">
         <v>90</v>
       </c>
@@ -1989,7 +1745,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="7"/>
-      <c r="B104" s="40"/>
+      <c r="B104" s="44"/>
       <c r="C104" s="8">
         <v>90</v>
       </c>
@@ -1998,72 +1754,72 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="7"/>
-      <c r="B105" s="40"/>
+      <c r="B105" s="44"/>
       <c r="C105" s="8">
         <v>90</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="8"/>
     </row>
-    <row r="106" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
-      <c r="B106" s="41"/>
+      <c r="B106" s="45"/>
       <c r="C106" s="10"/>
       <c r="D106" s="11"/>
       <c r="E106" s="10"/>
     </row>
-    <row r="107" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B107" s="36"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="37"/>
-      <c r="E107" s="38"/>
+      <c r="B107" s="40"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="42"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
-      <c r="B108" s="44"/>
+      <c r="B108" s="48"/>
       <c r="C108" s="5"/>
       <c r="D108" s="6"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7"/>
-      <c r="B109" s="40"/>
+      <c r="B109" s="44"/>
       <c r="C109" s="8"/>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7"/>
-      <c r="B110" s="40"/>
+      <c r="B110" s="44"/>
       <c r="C110" s="8"/>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7"/>
-      <c r="B111" s="40"/>
+      <c r="B111" s="44"/>
       <c r="C111" s="8"/>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
     </row>
-    <row r="112" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
-      <c r="B112" s="41"/>
+      <c r="B112" s="45"/>
       <c r="C112" s="10"/>
       <c r="D112" s="11"/>
       <c r="E112" s="10"/>
     </row>
-    <row r="113" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B113" s="36"/>
-      <c r="C113" s="37"/>
-      <c r="D113" s="37"/>
-      <c r="E113" s="38"/>
+      <c r="B113" s="40"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="42"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
@@ -2093,14 +1849,14 @@
       <c r="D117" s="31"/>
       <c r="E117" s="8"/>
     </row>
-    <row r="118" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8"/>
       <c r="B118" s="23"/>
       <c r="C118" s="8"/>
       <c r="D118" s="9"/>
       <c r="E118" s="8"/>
     </row>
-    <row r="119" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>16</v>
       </c>
@@ -2111,135 +1867,135 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
-      <c r="B120" s="44"/>
+      <c r="B120" s="48"/>
       <c r="C120" s="5"/>
       <c r="D120" s="6"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7"/>
-      <c r="B121" s="40"/>
+      <c r="B121" s="44"/>
       <c r="C121" s="8"/>
       <c r="D121" s="9"/>
       <c r="E121" s="8"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7"/>
-      <c r="B122" s="40"/>
+      <c r="B122" s="44"/>
       <c r="C122" s="8"/>
       <c r="D122" s="9"/>
       <c r="E122" s="8"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7"/>
-      <c r="B123" s="40"/>
+      <c r="B123" s="44"/>
       <c r="C123" s="8"/>
       <c r="D123" s="9"/>
       <c r="E123" s="8"/>
     </row>
-    <row r="124" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
-      <c r="B124" s="41"/>
+      <c r="B124" s="45"/>
       <c r="C124" s="10"/>
       <c r="D124" s="11"/>
       <c r="E124" s="10"/>
     </row>
-    <row r="125" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B125" s="36"/>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
-      <c r="E125" s="38"/>
+      <c r="B125" s="40"/>
+      <c r="C125" s="41"/>
+      <c r="D125" s="41"/>
+      <c r="E125" s="42"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
-      <c r="B126" s="44"/>
+      <c r="B126" s="48"/>
       <c r="C126" s="5"/>
       <c r="D126" s="6"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7"/>
-      <c r="B127" s="40"/>
+      <c r="B127" s="44"/>
       <c r="C127" s="8"/>
       <c r="D127" s="9"/>
       <c r="E127" s="8"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7"/>
-      <c r="B128" s="40"/>
+      <c r="B128" s="44"/>
       <c r="C128" s="8"/>
       <c r="D128" s="9"/>
       <c r="E128" s="8"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7"/>
-      <c r="B129" s="40"/>
+      <c r="B129" s="44"/>
       <c r="C129" s="8"/>
       <c r="D129" s="9"/>
       <c r="E129" s="8"/>
     </row>
-    <row r="130" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
-      <c r="B130" s="41"/>
+      <c r="B130" s="45"/>
       <c r="C130" s="10"/>
       <c r="D130" s="11"/>
       <c r="E130" s="10"/>
     </row>
-    <row r="131" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B131" s="36"/>
-      <c r="C131" s="37"/>
-      <c r="D131" s="37"/>
-      <c r="E131" s="38"/>
+      <c r="B131" s="40"/>
+      <c r="C131" s="41"/>
+      <c r="D131" s="41"/>
+      <c r="E131" s="42"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
-      <c r="B132" s="44"/>
+      <c r="B132" s="48"/>
       <c r="C132" s="5"/>
       <c r="D132" s="6"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7"/>
-      <c r="B133" s="40"/>
+      <c r="B133" s="44"/>
       <c r="C133" s="8"/>
       <c r="D133" s="9"/>
       <c r="E133" s="8"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
-      <c r="B134" s="40"/>
+      <c r="B134" s="44"/>
       <c r="C134" s="8"/>
       <c r="D134" s="9"/>
       <c r="E134" s="8"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7"/>
-      <c r="B135" s="40"/>
+      <c r="B135" s="44"/>
       <c r="C135" s="8"/>
       <c r="D135" s="9"/>
       <c r="E135" s="8"/>
     </row>
-    <row r="136" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
-      <c r="B136" s="41"/>
+      <c r="B136" s="45"/>
       <c r="C136" s="10"/>
       <c r="D136" s="11"/>
       <c r="E136" s="10"/>
     </row>
-    <row r="137" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B137" s="36"/>
-      <c r="C137" s="37"/>
-      <c r="D137" s="37"/>
-      <c r="E137" s="38"/>
+      <c r="B137" s="40"/>
+      <c r="C137" s="41"/>
+      <c r="D137" s="41"/>
+      <c r="E137" s="42"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
@@ -2269,14 +2025,14 @@
       <c r="D141" s="31"/>
       <c r="E141" s="8"/>
     </row>
-    <row r="142" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8"/>
       <c r="B142" s="23"/>
       <c r="C142" s="8"/>
       <c r="D142" s="9"/>
       <c r="E142" s="8"/>
     </row>
-    <row r="143" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>16</v>
       </c>
@@ -2287,135 +2043,135 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
-      <c r="B144" s="44"/>
+      <c r="B144" s="48"/>
       <c r="C144" s="5"/>
       <c r="D144" s="6"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7"/>
-      <c r="B145" s="40"/>
+      <c r="B145" s="44"/>
       <c r="C145" s="8"/>
       <c r="D145" s="9"/>
       <c r="E145" s="8"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7"/>
-      <c r="B146" s="40"/>
+      <c r="B146" s="44"/>
       <c r="C146" s="8"/>
       <c r="D146" s="9"/>
       <c r="E146" s="8"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7"/>
-      <c r="B147" s="40"/>
+      <c r="B147" s="44"/>
       <c r="C147" s="8"/>
       <c r="D147" s="9"/>
       <c r="E147" s="8"/>
     </row>
-    <row r="148" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
-      <c r="B148" s="41"/>
+      <c r="B148" s="45"/>
       <c r="C148" s="10"/>
       <c r="D148" s="11"/>
       <c r="E148" s="10"/>
     </row>
-    <row r="149" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B149" s="36"/>
-      <c r="C149" s="37"/>
-      <c r="D149" s="37"/>
-      <c r="E149" s="38"/>
+      <c r="B149" s="40"/>
+      <c r="C149" s="41"/>
+      <c r="D149" s="41"/>
+      <c r="E149" s="42"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
-      <c r="B150" s="44"/>
+      <c r="B150" s="48"/>
       <c r="C150" s="5"/>
       <c r="D150" s="6"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7"/>
-      <c r="B151" s="40"/>
+      <c r="B151" s="44"/>
       <c r="C151" s="8"/>
       <c r="D151" s="9"/>
       <c r="E151" s="8"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7"/>
-      <c r="B152" s="40"/>
+      <c r="B152" s="44"/>
       <c r="C152" s="8"/>
       <c r="D152" s="9"/>
       <c r="E152" s="8"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7"/>
-      <c r="B153" s="40"/>
+      <c r="B153" s="44"/>
       <c r="C153" s="8"/>
       <c r="D153" s="9"/>
       <c r="E153" s="8"/>
     </row>
-    <row r="154" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
-      <c r="B154" s="41"/>
+      <c r="B154" s="45"/>
       <c r="C154" s="10"/>
       <c r="D154" s="11"/>
       <c r="E154" s="10"/>
     </row>
-    <row r="155" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B155" s="36"/>
-      <c r="C155" s="37"/>
-      <c r="D155" s="37"/>
-      <c r="E155" s="38"/>
+      <c r="B155" s="40"/>
+      <c r="C155" s="41"/>
+      <c r="D155" s="41"/>
+      <c r="E155" s="42"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
-      <c r="B156" s="44"/>
+      <c r="B156" s="48"/>
       <c r="C156" s="5"/>
       <c r="D156" s="6"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7"/>
-      <c r="B157" s="40"/>
+      <c r="B157" s="44"/>
       <c r="C157" s="8"/>
       <c r="D157" s="9"/>
       <c r="E157" s="8"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7"/>
-      <c r="B158" s="40"/>
+      <c r="B158" s="44"/>
       <c r="C158" s="8"/>
       <c r="D158" s="9"/>
       <c r="E158" s="8"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7"/>
-      <c r="B159" s="40"/>
+      <c r="B159" s="44"/>
       <c r="C159" s="8"/>
       <c r="D159" s="9"/>
       <c r="E159" s="8"/>
     </row>
-    <row r="160" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
-      <c r="B160" s="41"/>
+      <c r="B160" s="45"/>
       <c r="C160" s="10"/>
       <c r="D160" s="11"/>
       <c r="E160" s="10"/>
     </row>
-    <row r="161" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B161" s="36"/>
-      <c r="C161" s="37"/>
-      <c r="D161" s="37"/>
-      <c r="E161" s="38"/>
+      <c r="B161" s="40"/>
+      <c r="C161" s="41"/>
+      <c r="D161" s="41"/>
+      <c r="E161" s="42"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="13"/>
@@ -2445,14 +2201,14 @@
       <c r="D165" s="31"/>
       <c r="E165" s="8"/>
     </row>
-    <row r="166" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8"/>
       <c r="B166" s="23"/>
       <c r="C166" s="8"/>
       <c r="D166" s="9"/>
       <c r="E166" s="8"/>
     </row>
-    <row r="167" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>16</v>
       </c>
@@ -2463,135 +2219,135 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
-      <c r="B168" s="44"/>
+      <c r="B168" s="48"/>
       <c r="C168" s="5"/>
       <c r="D168" s="6"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7"/>
-      <c r="B169" s="40"/>
+      <c r="B169" s="44"/>
       <c r="C169" s="8"/>
       <c r="D169" s="9"/>
       <c r="E169" s="8"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7"/>
-      <c r="B170" s="40"/>
+      <c r="B170" s="44"/>
       <c r="C170" s="8"/>
       <c r="D170" s="9"/>
       <c r="E170" s="8"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
-      <c r="B171" s="40"/>
+      <c r="B171" s="44"/>
       <c r="C171" s="8"/>
       <c r="D171" s="9"/>
       <c r="E171" s="8"/>
     </row>
-    <row r="172" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
-      <c r="B172" s="41"/>
+      <c r="B172" s="45"/>
       <c r="C172" s="10"/>
       <c r="D172" s="11"/>
       <c r="E172" s="10"/>
     </row>
-    <row r="173" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B173" s="36"/>
-      <c r="C173" s="37"/>
-      <c r="D173" s="37"/>
-      <c r="E173" s="38"/>
+      <c r="B173" s="40"/>
+      <c r="C173" s="41"/>
+      <c r="D173" s="41"/>
+      <c r="E173" s="42"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
-      <c r="B174" s="44"/>
+      <c r="B174" s="48"/>
       <c r="C174" s="5"/>
       <c r="D174" s="6"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7"/>
-      <c r="B175" s="40"/>
+      <c r="B175" s="44"/>
       <c r="C175" s="8"/>
       <c r="D175" s="9"/>
       <c r="E175" s="8"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
-      <c r="B176" s="40"/>
+      <c r="B176" s="44"/>
       <c r="C176" s="8"/>
       <c r="D176" s="9"/>
       <c r="E176" s="8"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
-      <c r="B177" s="40"/>
+      <c r="B177" s="44"/>
       <c r="C177" s="8"/>
       <c r="D177" s="9"/>
       <c r="E177" s="8"/>
     </row>
-    <row r="178" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
-      <c r="B178" s="41"/>
+      <c r="B178" s="45"/>
       <c r="C178" s="10"/>
       <c r="D178" s="11"/>
       <c r="E178" s="10"/>
     </row>
-    <row r="179" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B179" s="36"/>
-      <c r="C179" s="37"/>
-      <c r="D179" s="37"/>
-      <c r="E179" s="38"/>
+      <c r="B179" s="40"/>
+      <c r="C179" s="41"/>
+      <c r="D179" s="41"/>
+      <c r="E179" s="42"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
-      <c r="B180" s="44"/>
+      <c r="B180" s="48"/>
       <c r="C180" s="5"/>
       <c r="D180" s="6"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
-      <c r="B181" s="40"/>
+      <c r="B181" s="44"/>
       <c r="C181" s="8"/>
       <c r="D181" s="9"/>
       <c r="E181" s="8"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
-      <c r="B182" s="40"/>
+      <c r="B182" s="44"/>
       <c r="C182" s="8"/>
       <c r="D182" s="9"/>
       <c r="E182" s="8"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7"/>
-      <c r="B183" s="40"/>
+      <c r="B183" s="44"/>
       <c r="C183" s="8"/>
       <c r="D183" s="9"/>
       <c r="E183" s="8"/>
     </row>
-    <row r="184" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
-      <c r="B184" s="41"/>
+      <c r="B184" s="45"/>
       <c r="C184" s="10"/>
       <c r="D184" s="11"/>
       <c r="E184" s="10"/>
     </row>
-    <row r="185" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B185" s="36"/>
-      <c r="C185" s="37"/>
-      <c r="D185" s="37"/>
-      <c r="E185" s="38"/>
+      <c r="B185" s="40"/>
+      <c r="C185" s="41"/>
+      <c r="D185" s="41"/>
+      <c r="E185" s="42"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="13"/>
@@ -2621,14 +2377,14 @@
       <c r="D189" s="31"/>
       <c r="E189" s="8"/>
     </row>
-    <row r="190" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="8"/>
       <c r="B190" s="23"/>
       <c r="C190" s="8"/>
       <c r="D190" s="9"/>
       <c r="E190" s="8"/>
     </row>
-    <row r="191" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>16</v>
       </c>
@@ -2639,135 +2395,135 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
-      <c r="B192" s="44"/>
+      <c r="B192" s="48"/>
       <c r="C192" s="5"/>
       <c r="D192" s="6"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7"/>
-      <c r="B193" s="40"/>
+      <c r="B193" s="44"/>
       <c r="C193" s="8"/>
       <c r="D193" s="9"/>
       <c r="E193" s="8"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="7"/>
-      <c r="B194" s="40"/>
+      <c r="B194" s="44"/>
       <c r="C194" s="8"/>
       <c r="D194" s="9"/>
       <c r="E194" s="8"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7"/>
-      <c r="B195" s="40"/>
+      <c r="B195" s="44"/>
       <c r="C195" s="8"/>
       <c r="D195" s="9"/>
       <c r="E195" s="8"/>
     </row>
-    <row r="196" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="10"/>
-      <c r="B196" s="41"/>
+      <c r="B196" s="45"/>
       <c r="C196" s="10"/>
       <c r="D196" s="11"/>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B197" s="36"/>
-      <c r="C197" s="37"/>
-      <c r="D197" s="37"/>
-      <c r="E197" s="38"/>
+      <c r="B197" s="40"/>
+      <c r="C197" s="41"/>
+      <c r="D197" s="41"/>
+      <c r="E197" s="42"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
-      <c r="B198" s="44"/>
+      <c r="B198" s="48"/>
       <c r="C198" s="5"/>
       <c r="D198" s="6"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="7"/>
-      <c r="B199" s="40"/>
+      <c r="B199" s="44"/>
       <c r="C199" s="8"/>
       <c r="D199" s="9"/>
       <c r="E199" s="8"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="7"/>
-      <c r="B200" s="40"/>
+      <c r="B200" s="44"/>
       <c r="C200" s="8"/>
       <c r="D200" s="9"/>
       <c r="E200" s="8"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="7"/>
-      <c r="B201" s="40"/>
+      <c r="B201" s="44"/>
       <c r="C201" s="8"/>
       <c r="D201" s="9"/>
       <c r="E201" s="8"/>
     </row>
-    <row r="202" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="10"/>
-      <c r="B202" s="41"/>
+      <c r="B202" s="45"/>
       <c r="C202" s="10"/>
       <c r="D202" s="11"/>
       <c r="E202" s="10"/>
     </row>
-    <row r="203" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B203" s="36"/>
-      <c r="C203" s="37"/>
-      <c r="D203" s="37"/>
-      <c r="E203" s="38"/>
+      <c r="B203" s="40"/>
+      <c r="C203" s="41"/>
+      <c r="D203" s="41"/>
+      <c r="E203" s="42"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="44"/>
+      <c r="B204" s="48"/>
       <c r="C204" s="5"/>
       <c r="D204" s="6"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
-      <c r="B205" s="40"/>
+      <c r="B205" s="44"/>
       <c r="C205" s="8"/>
       <c r="D205" s="9"/>
       <c r="E205" s="8"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
-      <c r="B206" s="40"/>
+      <c r="B206" s="44"/>
       <c r="C206" s="8"/>
       <c r="D206" s="9"/>
       <c r="E206" s="8"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
-      <c r="B207" s="40"/>
+      <c r="B207" s="44"/>
       <c r="C207" s="8"/>
       <c r="D207" s="9"/>
       <c r="E207" s="8"/>
     </row>
-    <row r="208" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="10"/>
-      <c r="B208" s="41"/>
+      <c r="B208" s="45"/>
       <c r="C208" s="10"/>
       <c r="D208" s="11"/>
       <c r="E208" s="10"/>
     </row>
-    <row r="209" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B209" s="36"/>
-      <c r="C209" s="37"/>
-      <c r="D209" s="37"/>
-      <c r="E209" s="38"/>
+      <c r="B209" s="40"/>
+      <c r="C209" s="41"/>
+      <c r="D209" s="41"/>
+      <c r="E209" s="42"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="13"/>
@@ -2797,14 +2553,14 @@
       <c r="D213" s="31"/>
       <c r="E213" s="8"/>
     </row>
-    <row r="214" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="8"/>
       <c r="B214" s="23"/>
       <c r="C214" s="8"/>
       <c r="D214" s="9"/>
       <c r="E214" s="8"/>
     </row>
-    <row r="215" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
         <v>16</v>
       </c>
@@ -2815,135 +2571,135 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
-      <c r="B216" s="44"/>
+      <c r="B216" s="48"/>
       <c r="C216" s="5"/>
       <c r="D216" s="6"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="7"/>
-      <c r="B217" s="40"/>
+      <c r="B217" s="44"/>
       <c r="C217" s="8"/>
       <c r="D217" s="9"/>
       <c r="E217" s="8"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="7"/>
-      <c r="B218" s="40"/>
+      <c r="B218" s="44"/>
       <c r="C218" s="8"/>
       <c r="D218" s="9"/>
       <c r="E218" s="8"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="7"/>
-      <c r="B219" s="40"/>
+      <c r="B219" s="44"/>
       <c r="C219" s="8"/>
       <c r="D219" s="9"/>
       <c r="E219" s="8"/>
     </row>
-    <row r="220" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="10"/>
-      <c r="B220" s="41"/>
+      <c r="B220" s="45"/>
       <c r="C220" s="10"/>
       <c r="D220" s="11"/>
       <c r="E220" s="10"/>
     </row>
-    <row r="221" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B221" s="36"/>
-      <c r="C221" s="37"/>
-      <c r="D221" s="37"/>
-      <c r="E221" s="38"/>
+      <c r="B221" s="40"/>
+      <c r="C221" s="41"/>
+      <c r="D221" s="41"/>
+      <c r="E221" s="42"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
-      <c r="B222" s="44"/>
+      <c r="B222" s="48"/>
       <c r="C222" s="5"/>
       <c r="D222" s="6"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="7"/>
-      <c r="B223" s="40"/>
+      <c r="B223" s="44"/>
       <c r="C223" s="8"/>
       <c r="D223" s="9"/>
       <c r="E223" s="8"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="7"/>
-      <c r="B224" s="40"/>
+      <c r="B224" s="44"/>
       <c r="C224" s="8"/>
       <c r="D224" s="9"/>
       <c r="E224" s="8"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="7"/>
-      <c r="B225" s="40"/>
+      <c r="B225" s="44"/>
       <c r="C225" s="8"/>
       <c r="D225" s="9"/>
       <c r="E225" s="8"/>
     </row>
-    <row r="226" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="10"/>
-      <c r="B226" s="41"/>
+      <c r="B226" s="45"/>
       <c r="C226" s="10"/>
       <c r="D226" s="11"/>
       <c r="E226" s="10"/>
     </row>
-    <row r="227" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B227" s="36"/>
-      <c r="C227" s="37"/>
-      <c r="D227" s="37"/>
-      <c r="E227" s="38"/>
+      <c r="B227" s="40"/>
+      <c r="C227" s="41"/>
+      <c r="D227" s="41"/>
+      <c r="E227" s="42"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="4"/>
-      <c r="B228" s="44"/>
+      <c r="B228" s="48"/>
       <c r="C228" s="5"/>
       <c r="D228" s="6"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="7"/>
-      <c r="B229" s="40"/>
+      <c r="B229" s="44"/>
       <c r="C229" s="8"/>
       <c r="D229" s="9"/>
       <c r="E229" s="8"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="7"/>
-      <c r="B230" s="40"/>
+      <c r="B230" s="44"/>
       <c r="C230" s="8"/>
       <c r="D230" s="9"/>
       <c r="E230" s="8"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="7"/>
-      <c r="B231" s="40"/>
+      <c r="B231" s="44"/>
       <c r="C231" s="8"/>
       <c r="D231" s="9"/>
       <c r="E231" s="8"/>
     </row>
-    <row r="232" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
-      <c r="B232" s="41"/>
+      <c r="B232" s="45"/>
       <c r="C232" s="10"/>
       <c r="D232" s="11"/>
       <c r="E232" s="10"/>
     </row>
-    <row r="233" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B233" s="36"/>
-      <c r="C233" s="37"/>
-      <c r="D233" s="37"/>
-      <c r="E233" s="38"/>
+      <c r="B233" s="40"/>
+      <c r="C233" s="41"/>
+      <c r="D233" s="41"/>
+      <c r="E233" s="42"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="13"/>
@@ -2973,14 +2729,14 @@
       <c r="D237" s="31"/>
       <c r="E237" s="8"/>
     </row>
-    <row r="238" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="8"/>
       <c r="B238" s="23"/>
       <c r="C238" s="8"/>
       <c r="D238" s="9"/>
       <c r="E238" s="8"/>
     </row>
-    <row r="239" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12" t="s">
         <v>16</v>
       </c>
@@ -2989,7 +2745,7 @@
       <c r="D239" s="25"/>
       <c r="E239" s="26"/>
     </row>
-    <row r="240" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="27" t="s">
         <v>17</v>
       </c>
@@ -3002,19 +2758,17 @@
       <c r="E240" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E60:E63"/>
+  <mergeCells count="83">
     <mergeCell ref="E66:E69"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D6:D7"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E60:E63"/>
     <mergeCell ref="B156:B160"/>
     <mergeCell ref="B155:E155"/>
     <mergeCell ref="B150:B154"/>
@@ -3097,28 +2851,14 @@
       <formula1>45261</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="E8:E9" r:id="rId1" display="CDC" xr:uid="{8A31EDA6-9493-4CD3-950D-6D91BB4DB18D}"/>
-    <hyperlink ref="E12:E13" r:id="rId2" display="Git" xr:uid="{9CBA37E5-3AA6-4637-9889-CEBD025EEA0B}"/>
-    <hyperlink ref="E14:E15" r:id="rId3" display="Git" xr:uid="{2F291771-AEC4-4659-91B0-1458296540CF}"/>
-    <hyperlink ref="E18" r:id="rId4" display="Git" xr:uid="{BA6FC8CD-CE40-46F4-AD9C-C7500FB16BB3}"/>
-    <hyperlink ref="E20:E21" r:id="rId5" display="Git/camera" xr:uid="{A3F2175C-4EB5-4E81-A42C-ED77BD1E2E5B}"/>
-    <hyperlink ref="E26:E27" r:id="rId6" display="Git/enigmes" xr:uid="{2315CA4F-6B4A-459E-81A1-B30CC3379F29}"/>
-    <hyperlink ref="E30:E33" r:id="rId7" display="Git/enigmes" xr:uid="{F3EB6F35-2194-4428-9201-905503D6C610}"/>
-    <hyperlink ref="E38:E39" r:id="rId8" display="Git/enigmes" xr:uid="{D188C66F-BD91-4187-AD0B-69AFD8BD7E0C}"/>
-    <hyperlink ref="E42:E45" r:id="rId9" display="Git" xr:uid="{488EBB5B-87D3-4375-B770-18EE2FB8B134}"/>
-    <hyperlink ref="E48:E51" r:id="rId10" display="Git" xr:uid="{973EA19B-C6B4-4AE8-AC22-005CB8992AE4}"/>
-    <hyperlink ref="E60:E63" r:id="rId11" display="Eloquent JavaScript" xr:uid="{22923CB4-6581-4F5E-8373-A8F65CAA6AD8}"/>
-    <hyperlink ref="E66:E69" r:id="rId12" display="Eloquent JavaScript" xr:uid="{498C12CB-03AE-4332-9BC8-56C2FE6309C4}"/>
-  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Etml_font,Normal"&amp;22ETML&amp;R&amp;G</oddHeader>
     <oddFooter>&amp;L&amp;14&amp;D&amp;R&amp;14Journal</oddFooter>
   </headerFooter>
-  <legacyDrawingHF r:id="rId14"/>
+  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/doc/jdt.xlsx
+++ b/doc/jdt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pa22yog\Documents\GitHub\Shoot-em-up-i320\Shoot-em-UP-game\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D1097A-D7C7-420C-8BEE-87E8BD330840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2394F909-4EDD-4FC6-9BFF-729DB76E0D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Journal" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="Rapport">Journal!$E$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$E$72</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Apprenti.e</t>
   </si>
@@ -54,9 +55,6 @@
   </si>
   <si>
     <t>Classe ou Groupe</t>
-  </si>
-  <si>
-    <t>MIN1B</t>
   </si>
   <si>
     <t>Experts </t>
@@ -116,6 +114,36 @@
   </si>
   <si>
     <t>Création de prémier User Story</t>
+  </si>
+  <si>
+    <t>Discussion sur le projet avec le professeur</t>
+  </si>
+  <si>
+    <t>Conception des User Storys pour un jeu</t>
+  </si>
+  <si>
+    <t>MID2B</t>
+  </si>
+  <si>
+    <t>Xavier Carrel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travail sur le rapport </t>
+  </si>
+  <si>
+    <t>Rapport</t>
+  </si>
+  <si>
+    <t>Git - User Storys</t>
+  </si>
+  <si>
+    <t>Git - User Story 1</t>
+  </si>
+  <si>
+    <t>Repos GitHub</t>
+  </si>
+  <si>
+    <t>CDC</t>
   </si>
 </sst>
 </file>
@@ -353,7 +381,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -477,6 +505,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -489,85 +579,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -900,10 +941,10 @@
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="52"/>
       <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
@@ -915,550 +956,576 @@
       <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="21" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="21" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
+        <v>9</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
-      <c r="B6" s="43">
+      <c r="B6" s="46">
         <v>46262</v>
       </c>
       <c r="C6" s="5">
         <v>100</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="44"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="8">
         <v>20</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="44"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="8">
         <v>30</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="57"/>
-    </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="E8" s="62"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="44"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="8">
         <v>30</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="56"/>
+        <v>20</v>
+      </c>
+      <c r="E9" s="64" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
-      <c r="B10" s="45"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="45"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="54"/>
+      <c r="B12" s="46">
+        <v>46269</v>
+      </c>
+      <c r="C12" s="5">
+        <v>30</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="60"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="56"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="8">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="64" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="57"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="8">
+        <v>70</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="44"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="56"/>
+      <c r="E15" s="61"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="45"/>
+      <c r="B16" s="42"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="43"/>
+      <c r="B18" s="46"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
       <c r="E18" s="33"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
-      <c r="B19" s="44"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="8"/>
       <c r="D19" s="30"/>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="44"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="57"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="39"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="44"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="56"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
-      <c r="B22" s="45"/>
+      <c r="B22" s="42"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
       <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="45"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="43"/>
+      <c r="B24" s="46"/>
       <c r="C24" s="5"/>
       <c r="D24"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
-      <c r="B25" s="44"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="44"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="57"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="39"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="44"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="56"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="38"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
-      <c r="B28" s="45"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
       <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="45"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
-      <c r="B30" s="43"/>
+      <c r="B30" s="46"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="54"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="36"/>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="44"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="55"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="37"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="44"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="55"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="37"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="44"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="56"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
-      <c r="B34" s="45"/>
+      <c r="B34" s="42"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="43"/>
+      <c r="B36" s="46"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
-      <c r="B37" s="44"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
-      <c r="B38" s="44"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="57"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="39"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
-      <c r="B39" s="44"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="56"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="38"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
-      <c r="B40" s="45"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
       <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B41" s="43"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="45"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="43"/>
+      <c r="B42" s="46"/>
       <c r="C42" s="5"/>
       <c r="D42"/>
-      <c r="E42" s="54"/>
+      <c r="E42" s="36"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
-      <c r="B43" s="44"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="8"/>
       <c r="D43"/>
-      <c r="E43" s="55"/>
+      <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
-      <c r="B44" s="44"/>
+      <c r="B44" s="41"/>
       <c r="C44" s="8"/>
       <c r="D44"/>
-      <c r="E44" s="55"/>
+      <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
-      <c r="B45" s="44"/>
+      <c r="B45" s="41"/>
       <c r="C45" s="8"/>
       <c r="D45"/>
-      <c r="E45" s="56"/>
+      <c r="E45" s="38"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="45"/>
+      <c r="B46" s="42"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11"/>
       <c r="E46" s="10"/>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="40"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B47" s="43"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="43"/>
+      <c r="B48" s="46"/>
       <c r="C48" s="5"/>
       <c r="D48"/>
-      <c r="E48" s="54"/>
+      <c r="E48" s="36"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
-      <c r="B49" s="44"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="8"/>
       <c r="D49"/>
-      <c r="E49" s="55"/>
+      <c r="E49" s="37"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
-      <c r="B50" s="44"/>
+      <c r="B50" s="41"/>
       <c r="C50" s="8"/>
       <c r="D50"/>
-      <c r="E50" s="55"/>
+      <c r="E50" s="37"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
-      <c r="B51" s="44"/>
+      <c r="B51" s="41"/>
       <c r="C51" s="8"/>
       <c r="D51"/>
-      <c r="E51" s="56"/>
+      <c r="E51" s="38"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
-      <c r="B52" s="45"/>
+      <c r="B52" s="42"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="10"/>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B53" s="43"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="45"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
-      <c r="B54" s="43"/>
+      <c r="B54" s="46"/>
       <c r="C54" s="5"/>
       <c r="D54"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
-      <c r="B55" s="44"/>
+      <c r="B55" s="41"/>
       <c r="C55" s="8"/>
       <c r="D55"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
-      <c r="B56" s="44"/>
+      <c r="B56" s="41"/>
       <c r="C56" s="8"/>
       <c r="D56"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
-      <c r="B57" s="44"/>
+      <c r="B57" s="41"/>
       <c r="C57" s="8"/>
       <c r="D57"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
-      <c r="B58" s="45"/>
+      <c r="B58" s="42"/>
       <c r="C58" s="10"/>
       <c r="D58" s="11"/>
       <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B59" s="40"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B59" s="43"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="45"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
-      <c r="B60" s="43"/>
+      <c r="B60" s="46"/>
       <c r="C60" s="5"/>
       <c r="D60" s="6"/>
-      <c r="E60" s="54"/>
+      <c r="E60" s="36"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
-      <c r="B61" s="44"/>
+      <c r="B61" s="41"/>
       <c r="C61" s="8"/>
       <c r="D61" s="6"/>
-      <c r="E61" s="55"/>
+      <c r="E61" s="37"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
-      <c r="B62" s="44"/>
+      <c r="B62" s="41"/>
       <c r="C62" s="8"/>
       <c r="D62" s="6"/>
-      <c r="E62" s="55"/>
+      <c r="E62" s="37"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
-      <c r="B63" s="44"/>
+      <c r="B63" s="41"/>
       <c r="C63" s="8"/>
       <c r="D63" s="6"/>
-      <c r="E63" s="56"/>
+      <c r="E63" s="38"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
-      <c r="B64" s="45"/>
+      <c r="B64" s="42"/>
       <c r="C64" s="10"/>
       <c r="D64" s="11"/>
       <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B65" s="40"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B65" s="43"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="45"/>
     </row>
     <row r="66" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
-      <c r="B66" s="43"/>
+      <c r="B66" s="46"/>
       <c r="C66" s="5"/>
       <c r="D66" s="14"/>
-      <c r="E66" s="54"/>
+      <c r="E66" s="36"/>
     </row>
     <row r="67" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
-      <c r="B67" s="44"/>
+      <c r="B67" s="41"/>
       <c r="C67" s="8"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="55"/>
+      <c r="E67" s="37"/>
     </row>
     <row r="68" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
-      <c r="B68" s="44"/>
+      <c r="B68" s="41"/>
       <c r="C68" s="8"/>
       <c r="D68" s="6"/>
-      <c r="E68" s="55"/>
+      <c r="E68" s="37"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
-      <c r="B69" s="44"/>
+      <c r="B69" s="41"/>
       <c r="C69" s="8"/>
       <c r="D69" s="6"/>
-      <c r="E69" s="56"/>
+      <c r="E69" s="38"/>
     </row>
     <row r="70" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
-      <c r="B70" s="45"/>
+      <c r="B70" s="42"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B71" s="24"/>
       <c r="C71" s="25"/>
@@ -1467,7 +1534,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
-      <c r="B72" s="48"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="5">
         <v>90</v>
       </c>
@@ -1476,7 +1543,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
-      <c r="B73" s="44"/>
+      <c r="B73" s="41"/>
       <c r="C73" s="8">
         <v>90</v>
       </c>
@@ -1485,7 +1552,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
-      <c r="B74" s="44"/>
+      <c r="B74" s="41"/>
       <c r="C74" s="8">
         <v>90</v>
       </c>
@@ -1494,7 +1561,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
-      <c r="B75" s="44"/>
+      <c r="B75" s="41"/>
       <c r="C75" s="8">
         <v>90</v>
       </c>
@@ -1503,23 +1570,23 @@
     </row>
     <row r="76" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
-      <c r="B76" s="45"/>
+      <c r="B76" s="42"/>
       <c r="C76" s="10"/>
       <c r="D76" s="11"/>
       <c r="E76" s="10"/>
     </row>
     <row r="77" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B77" s="40"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B77" s="43"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="45"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="13"/>
-      <c r="B78" s="48"/>
+      <c r="B78" s="40"/>
       <c r="C78" s="5">
         <v>90</v>
       </c>
@@ -1528,7 +1595,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="8"/>
-      <c r="B79" s="44"/>
+      <c r="B79" s="41"/>
       <c r="C79" s="8">
         <v>90</v>
       </c>
@@ -1537,7 +1604,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="8"/>
-      <c r="B80" s="44"/>
+      <c r="B80" s="41"/>
       <c r="C80" s="8">
         <v>90</v>
       </c>
@@ -1546,7 +1613,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="8"/>
-      <c r="B81" s="44"/>
+      <c r="B81" s="41"/>
       <c r="C81" s="8">
         <v>90</v>
       </c>
@@ -1555,23 +1622,23 @@
     </row>
     <row r="82" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
-      <c r="B82" s="45"/>
+      <c r="B82" s="42"/>
       <c r="C82" s="10"/>
       <c r="D82" s="11"/>
       <c r="E82" s="10"/>
     </row>
     <row r="83" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B83" s="40"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B83" s="43"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="45"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
-      <c r="B84" s="48"/>
+      <c r="B84" s="40"/>
       <c r="C84" s="5">
         <v>90</v>
       </c>
@@ -1580,7 +1647,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
-      <c r="B85" s="44"/>
+      <c r="B85" s="41"/>
       <c r="C85" s="8">
         <v>90</v>
       </c>
@@ -1589,7 +1656,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
-      <c r="B86" s="44"/>
+      <c r="B86" s="41"/>
       <c r="C86" s="8">
         <v>90</v>
       </c>
@@ -1598,7 +1665,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
-      <c r="B87" s="44"/>
+      <c r="B87" s="41"/>
       <c r="C87" s="8">
         <v>90</v>
       </c>
@@ -1607,19 +1674,19 @@
     </row>
     <row r="88" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
-      <c r="B88" s="45"/>
+      <c r="B88" s="42"/>
       <c r="C88" s="10"/>
       <c r="D88" s="11"/>
       <c r="E88" s="10"/>
     </row>
     <row r="89" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B89" s="40"/>
-      <c r="C89" s="41"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B89" s="43"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="45"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
@@ -1666,7 +1733,7 @@
     </row>
     <row r="95" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B95" s="24"/>
       <c r="C95" s="25"/>
@@ -1675,7 +1742,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
-      <c r="B96" s="48"/>
+      <c r="B96" s="40"/>
       <c r="C96" s="5">
         <v>90</v>
       </c>
@@ -1684,7 +1751,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
-      <c r="B97" s="44"/>
+      <c r="B97" s="41"/>
       <c r="C97" s="8">
         <v>90</v>
       </c>
@@ -1693,7 +1760,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
-      <c r="B98" s="44"/>
+      <c r="B98" s="41"/>
       <c r="C98" s="8">
         <v>90</v>
       </c>
@@ -1702,7 +1769,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7"/>
-      <c r="B99" s="44"/>
+      <c r="B99" s="41"/>
       <c r="C99" s="8">
         <v>90</v>
       </c>
@@ -1711,23 +1778,23 @@
     </row>
     <row r="100" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
-      <c r="B100" s="45"/>
+      <c r="B100" s="42"/>
       <c r="C100" s="10"/>
       <c r="D100" s="11"/>
       <c r="E100" s="10"/>
     </row>
     <row r="101" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B101" s="40"/>
-      <c r="C101" s="41"/>
-      <c r="D101" s="41"/>
-      <c r="E101" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B101" s="43"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="45"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="4"/>
-      <c r="B102" s="48"/>
+      <c r="B102" s="40"/>
       <c r="C102" s="5">
         <v>90</v>
       </c>
@@ -1736,7 +1803,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7"/>
-      <c r="B103" s="44"/>
+      <c r="B103" s="41"/>
       <c r="C103" s="8">
         <v>90</v>
       </c>
@@ -1745,7 +1812,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="7"/>
-      <c r="B104" s="44"/>
+      <c r="B104" s="41"/>
       <c r="C104" s="8">
         <v>90</v>
       </c>
@@ -1754,7 +1821,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="7"/>
-      <c r="B105" s="44"/>
+      <c r="B105" s="41"/>
       <c r="C105" s="8">
         <v>90</v>
       </c>
@@ -1763,63 +1830,63 @@
     </row>
     <row r="106" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
-      <c r="B106" s="45"/>
+      <c r="B106" s="42"/>
       <c r="C106" s="10"/>
       <c r="D106" s="11"/>
       <c r="E106" s="10"/>
     </row>
     <row r="107" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B107" s="40"/>
-      <c r="C107" s="41"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B107" s="43"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="45"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
-      <c r="B108" s="48"/>
+      <c r="B108" s="40"/>
       <c r="C108" s="5"/>
       <c r="D108" s="6"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7"/>
-      <c r="B109" s="44"/>
+      <c r="B109" s="41"/>
       <c r="C109" s="8"/>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7"/>
-      <c r="B110" s="44"/>
+      <c r="B110" s="41"/>
       <c r="C110" s="8"/>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7"/>
-      <c r="B111" s="44"/>
+      <c r="B111" s="41"/>
       <c r="C111" s="8"/>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
     </row>
     <row r="112" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
-      <c r="B112" s="45"/>
+      <c r="B112" s="42"/>
       <c r="C112" s="10"/>
       <c r="D112" s="11"/>
       <c r="E112" s="10"/>
     </row>
     <row r="113" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B113" s="40"/>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B113" s="43"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="45"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
@@ -1858,7 +1925,7 @@
     </row>
     <row r="119" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B119" s="24"/>
       <c r="C119" s="25"/>
@@ -1867,135 +1934,135 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
-      <c r="B120" s="48"/>
+      <c r="B120" s="40"/>
       <c r="C120" s="5"/>
       <c r="D120" s="6"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7"/>
-      <c r="B121" s="44"/>
+      <c r="B121" s="41"/>
       <c r="C121" s="8"/>
       <c r="D121" s="9"/>
       <c r="E121" s="8"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7"/>
-      <c r="B122" s="44"/>
+      <c r="B122" s="41"/>
       <c r="C122" s="8"/>
       <c r="D122" s="9"/>
       <c r="E122" s="8"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7"/>
-      <c r="B123" s="44"/>
+      <c r="B123" s="41"/>
       <c r="C123" s="8"/>
       <c r="D123" s="9"/>
       <c r="E123" s="8"/>
     </row>
     <row r="124" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
-      <c r="B124" s="45"/>
+      <c r="B124" s="42"/>
       <c r="C124" s="10"/>
       <c r="D124" s="11"/>
       <c r="E124" s="10"/>
     </row>
     <row r="125" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B125" s="40"/>
-      <c r="C125" s="41"/>
-      <c r="D125" s="41"/>
-      <c r="E125" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B125" s="43"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="45"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
-      <c r="B126" s="48"/>
+      <c r="B126" s="40"/>
       <c r="C126" s="5"/>
       <c r="D126" s="6"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7"/>
-      <c r="B127" s="44"/>
+      <c r="B127" s="41"/>
       <c r="C127" s="8"/>
       <c r="D127" s="9"/>
       <c r="E127" s="8"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7"/>
-      <c r="B128" s="44"/>
+      <c r="B128" s="41"/>
       <c r="C128" s="8"/>
       <c r="D128" s="9"/>
       <c r="E128" s="8"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7"/>
-      <c r="B129" s="44"/>
+      <c r="B129" s="41"/>
       <c r="C129" s="8"/>
       <c r="D129" s="9"/>
       <c r="E129" s="8"/>
     </row>
     <row r="130" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
-      <c r="B130" s="45"/>
+      <c r="B130" s="42"/>
       <c r="C130" s="10"/>
       <c r="D130" s="11"/>
       <c r="E130" s="10"/>
     </row>
     <row r="131" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B131" s="40"/>
-      <c r="C131" s="41"/>
-      <c r="D131" s="41"/>
-      <c r="E131" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B131" s="43"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="45"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
-      <c r="B132" s="48"/>
+      <c r="B132" s="40"/>
       <c r="C132" s="5"/>
       <c r="D132" s="6"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7"/>
-      <c r="B133" s="44"/>
+      <c r="B133" s="41"/>
       <c r="C133" s="8"/>
       <c r="D133" s="9"/>
       <c r="E133" s="8"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
-      <c r="B134" s="44"/>
+      <c r="B134" s="41"/>
       <c r="C134" s="8"/>
       <c r="D134" s="9"/>
       <c r="E134" s="8"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7"/>
-      <c r="B135" s="44"/>
+      <c r="B135" s="41"/>
       <c r="C135" s="8"/>
       <c r="D135" s="9"/>
       <c r="E135" s="8"/>
     </row>
     <row r="136" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
-      <c r="B136" s="45"/>
+      <c r="B136" s="42"/>
       <c r="C136" s="10"/>
       <c r="D136" s="11"/>
       <c r="E136" s="10"/>
     </row>
     <row r="137" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B137" s="40"/>
-      <c r="C137" s="41"/>
-      <c r="D137" s="41"/>
-      <c r="E137" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B137" s="43"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="45"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="13"/>
@@ -2034,7 +2101,7 @@
     </row>
     <row r="143" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B143" s="24"/>
       <c r="C143" s="25"/>
@@ -2043,135 +2110,135 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
-      <c r="B144" s="48"/>
+      <c r="B144" s="40"/>
       <c r="C144" s="5"/>
       <c r="D144" s="6"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7"/>
-      <c r="B145" s="44"/>
+      <c r="B145" s="41"/>
       <c r="C145" s="8"/>
       <c r="D145" s="9"/>
       <c r="E145" s="8"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7"/>
-      <c r="B146" s="44"/>
+      <c r="B146" s="41"/>
       <c r="C146" s="8"/>
       <c r="D146" s="9"/>
       <c r="E146" s="8"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7"/>
-      <c r="B147" s="44"/>
+      <c r="B147" s="41"/>
       <c r="C147" s="8"/>
       <c r="D147" s="9"/>
       <c r="E147" s="8"/>
     </row>
     <row r="148" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
-      <c r="B148" s="45"/>
+      <c r="B148" s="42"/>
       <c r="C148" s="10"/>
       <c r="D148" s="11"/>
       <c r="E148" s="10"/>
     </row>
     <row r="149" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B149" s="40"/>
-      <c r="C149" s="41"/>
-      <c r="D149" s="41"/>
-      <c r="E149" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B149" s="43"/>
+      <c r="C149" s="44"/>
+      <c r="D149" s="44"/>
+      <c r="E149" s="45"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
-      <c r="B150" s="48"/>
+      <c r="B150" s="40"/>
       <c r="C150" s="5"/>
       <c r="D150" s="6"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7"/>
-      <c r="B151" s="44"/>
+      <c r="B151" s="41"/>
       <c r="C151" s="8"/>
       <c r="D151" s="9"/>
       <c r="E151" s="8"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7"/>
-      <c r="B152" s="44"/>
+      <c r="B152" s="41"/>
       <c r="C152" s="8"/>
       <c r="D152" s="9"/>
       <c r="E152" s="8"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7"/>
-      <c r="B153" s="44"/>
+      <c r="B153" s="41"/>
       <c r="C153" s="8"/>
       <c r="D153" s="9"/>
       <c r="E153" s="8"/>
     </row>
     <row r="154" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
-      <c r="B154" s="45"/>
+      <c r="B154" s="42"/>
       <c r="C154" s="10"/>
       <c r="D154" s="11"/>
       <c r="E154" s="10"/>
     </row>
     <row r="155" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B155" s="40"/>
-      <c r="C155" s="41"/>
-      <c r="D155" s="41"/>
-      <c r="E155" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B155" s="43"/>
+      <c r="C155" s="44"/>
+      <c r="D155" s="44"/>
+      <c r="E155" s="45"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
-      <c r="B156" s="48"/>
+      <c r="B156" s="40"/>
       <c r="C156" s="5"/>
       <c r="D156" s="6"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7"/>
-      <c r="B157" s="44"/>
+      <c r="B157" s="41"/>
       <c r="C157" s="8"/>
       <c r="D157" s="9"/>
       <c r="E157" s="8"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7"/>
-      <c r="B158" s="44"/>
+      <c r="B158" s="41"/>
       <c r="C158" s="8"/>
       <c r="D158" s="9"/>
       <c r="E158" s="8"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7"/>
-      <c r="B159" s="44"/>
+      <c r="B159" s="41"/>
       <c r="C159" s="8"/>
       <c r="D159" s="9"/>
       <c r="E159" s="8"/>
     </row>
     <row r="160" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
-      <c r="B160" s="45"/>
+      <c r="B160" s="42"/>
       <c r="C160" s="10"/>
       <c r="D160" s="11"/>
       <c r="E160" s="10"/>
     </row>
     <row r="161" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B161" s="40"/>
-      <c r="C161" s="41"/>
-      <c r="D161" s="41"/>
-      <c r="E161" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B161" s="43"/>
+      <c r="C161" s="44"/>
+      <c r="D161" s="44"/>
+      <c r="E161" s="45"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="13"/>
@@ -2210,7 +2277,7 @@
     </row>
     <row r="167" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B167" s="24"/>
       <c r="C167" s="25"/>
@@ -2219,135 +2286,135 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
-      <c r="B168" s="48"/>
+      <c r="B168" s="40"/>
       <c r="C168" s="5"/>
       <c r="D168" s="6"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7"/>
-      <c r="B169" s="44"/>
+      <c r="B169" s="41"/>
       <c r="C169" s="8"/>
       <c r="D169" s="9"/>
       <c r="E169" s="8"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7"/>
-      <c r="B170" s="44"/>
+      <c r="B170" s="41"/>
       <c r="C170" s="8"/>
       <c r="D170" s="9"/>
       <c r="E170" s="8"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
-      <c r="B171" s="44"/>
+      <c r="B171" s="41"/>
       <c r="C171" s="8"/>
       <c r="D171" s="9"/>
       <c r="E171" s="8"/>
     </row>
     <row r="172" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
-      <c r="B172" s="45"/>
+      <c r="B172" s="42"/>
       <c r="C172" s="10"/>
       <c r="D172" s="11"/>
       <c r="E172" s="10"/>
     </row>
     <row r="173" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B173" s="40"/>
-      <c r="C173" s="41"/>
-      <c r="D173" s="41"/>
-      <c r="E173" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B173" s="43"/>
+      <c r="C173" s="44"/>
+      <c r="D173" s="44"/>
+      <c r="E173" s="45"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
-      <c r="B174" s="48"/>
+      <c r="B174" s="40"/>
       <c r="C174" s="5"/>
       <c r="D174" s="6"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7"/>
-      <c r="B175" s="44"/>
+      <c r="B175" s="41"/>
       <c r="C175" s="8"/>
       <c r="D175" s="9"/>
       <c r="E175" s="8"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
-      <c r="B176" s="44"/>
+      <c r="B176" s="41"/>
       <c r="C176" s="8"/>
       <c r="D176" s="9"/>
       <c r="E176" s="8"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
-      <c r="B177" s="44"/>
+      <c r="B177" s="41"/>
       <c r="C177" s="8"/>
       <c r="D177" s="9"/>
       <c r="E177" s="8"/>
     </row>
     <row r="178" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
-      <c r="B178" s="45"/>
+      <c r="B178" s="42"/>
       <c r="C178" s="10"/>
       <c r="D178" s="11"/>
       <c r="E178" s="10"/>
     </row>
     <row r="179" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B179" s="40"/>
-      <c r="C179" s="41"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B179" s="43"/>
+      <c r="C179" s="44"/>
+      <c r="D179" s="44"/>
+      <c r="E179" s="45"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
-      <c r="B180" s="48"/>
+      <c r="B180" s="40"/>
       <c r="C180" s="5"/>
       <c r="D180" s="6"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
-      <c r="B181" s="44"/>
+      <c r="B181" s="41"/>
       <c r="C181" s="8"/>
       <c r="D181" s="9"/>
       <c r="E181" s="8"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
-      <c r="B182" s="44"/>
+      <c r="B182" s="41"/>
       <c r="C182" s="8"/>
       <c r="D182" s="9"/>
       <c r="E182" s="8"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7"/>
-      <c r="B183" s="44"/>
+      <c r="B183" s="41"/>
       <c r="C183" s="8"/>
       <c r="D183" s="9"/>
       <c r="E183" s="8"/>
     </row>
     <row r="184" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
-      <c r="B184" s="45"/>
+      <c r="B184" s="42"/>
       <c r="C184" s="10"/>
       <c r="D184" s="11"/>
       <c r="E184" s="10"/>
     </row>
     <row r="185" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B185" s="40"/>
-      <c r="C185" s="41"/>
-      <c r="D185" s="41"/>
-      <c r="E185" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B185" s="43"/>
+      <c r="C185" s="44"/>
+      <c r="D185" s="44"/>
+      <c r="E185" s="45"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="13"/>
@@ -2386,7 +2453,7 @@
     </row>
     <row r="191" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B191" s="24"/>
       <c r="C191" s="25"/>
@@ -2395,135 +2462,135 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
-      <c r="B192" s="48"/>
+      <c r="B192" s="40"/>
       <c r="C192" s="5"/>
       <c r="D192" s="6"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7"/>
-      <c r="B193" s="44"/>
+      <c r="B193" s="41"/>
       <c r="C193" s="8"/>
       <c r="D193" s="9"/>
       <c r="E193" s="8"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="7"/>
-      <c r="B194" s="44"/>
+      <c r="B194" s="41"/>
       <c r="C194" s="8"/>
       <c r="D194" s="9"/>
       <c r="E194" s="8"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7"/>
-      <c r="B195" s="44"/>
+      <c r="B195" s="41"/>
       <c r="C195" s="8"/>
       <c r="D195" s="9"/>
       <c r="E195" s="8"/>
     </row>
     <row r="196" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="10"/>
-      <c r="B196" s="45"/>
+      <c r="B196" s="42"/>
       <c r="C196" s="10"/>
       <c r="D196" s="11"/>
       <c r="E196" s="10"/>
     </row>
     <row r="197" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B197" s="40"/>
-      <c r="C197" s="41"/>
-      <c r="D197" s="41"/>
-      <c r="E197" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B197" s="43"/>
+      <c r="C197" s="44"/>
+      <c r="D197" s="44"/>
+      <c r="E197" s="45"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
-      <c r="B198" s="48"/>
+      <c r="B198" s="40"/>
       <c r="C198" s="5"/>
       <c r="D198" s="6"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="7"/>
-      <c r="B199" s="44"/>
+      <c r="B199" s="41"/>
       <c r="C199" s="8"/>
       <c r="D199" s="9"/>
       <c r="E199" s="8"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="7"/>
-      <c r="B200" s="44"/>
+      <c r="B200" s="41"/>
       <c r="C200" s="8"/>
       <c r="D200" s="9"/>
       <c r="E200" s="8"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="7"/>
-      <c r="B201" s="44"/>
+      <c r="B201" s="41"/>
       <c r="C201" s="8"/>
       <c r="D201" s="9"/>
       <c r="E201" s="8"/>
     </row>
     <row r="202" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="10"/>
-      <c r="B202" s="45"/>
+      <c r="B202" s="42"/>
       <c r="C202" s="10"/>
       <c r="D202" s="11"/>
       <c r="E202" s="10"/>
     </row>
     <row r="203" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B203" s="40"/>
-      <c r="C203" s="41"/>
-      <c r="D203" s="41"/>
-      <c r="E203" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B203" s="43"/>
+      <c r="C203" s="44"/>
+      <c r="D203" s="44"/>
+      <c r="E203" s="45"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="48"/>
+      <c r="B204" s="40"/>
       <c r="C204" s="5"/>
       <c r="D204" s="6"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
-      <c r="B205" s="44"/>
+      <c r="B205" s="41"/>
       <c r="C205" s="8"/>
       <c r="D205" s="9"/>
       <c r="E205" s="8"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
-      <c r="B206" s="44"/>
+      <c r="B206" s="41"/>
       <c r="C206" s="8"/>
       <c r="D206" s="9"/>
       <c r="E206" s="8"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
-      <c r="B207" s="44"/>
+      <c r="B207" s="41"/>
       <c r="C207" s="8"/>
       <c r="D207" s="9"/>
       <c r="E207" s="8"/>
     </row>
     <row r="208" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="10"/>
-      <c r="B208" s="45"/>
+      <c r="B208" s="42"/>
       <c r="C208" s="10"/>
       <c r="D208" s="11"/>
       <c r="E208" s="10"/>
     </row>
     <row r="209" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B209" s="40"/>
-      <c r="C209" s="41"/>
-      <c r="D209" s="41"/>
-      <c r="E209" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B209" s="43"/>
+      <c r="C209" s="44"/>
+      <c r="D209" s="44"/>
+      <c r="E209" s="45"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="13"/>
@@ -2562,7 +2629,7 @@
     </row>
     <row r="215" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B215" s="24"/>
       <c r="C215" s="25"/>
@@ -2571,135 +2638,135 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
-      <c r="B216" s="48"/>
+      <c r="B216" s="40"/>
       <c r="C216" s="5"/>
       <c r="D216" s="6"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="7"/>
-      <c r="B217" s="44"/>
+      <c r="B217" s="41"/>
       <c r="C217" s="8"/>
       <c r="D217" s="9"/>
       <c r="E217" s="8"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="7"/>
-      <c r="B218" s="44"/>
+      <c r="B218" s="41"/>
       <c r="C218" s="8"/>
       <c r="D218" s="9"/>
       <c r="E218" s="8"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="7"/>
-      <c r="B219" s="44"/>
+      <c r="B219" s="41"/>
       <c r="C219" s="8"/>
       <c r="D219" s="9"/>
       <c r="E219" s="8"/>
     </row>
     <row r="220" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="10"/>
-      <c r="B220" s="45"/>
+      <c r="B220" s="42"/>
       <c r="C220" s="10"/>
       <c r="D220" s="11"/>
       <c r="E220" s="10"/>
     </row>
     <row r="221" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B221" s="40"/>
-      <c r="C221" s="41"/>
-      <c r="D221" s="41"/>
-      <c r="E221" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B221" s="43"/>
+      <c r="C221" s="44"/>
+      <c r="D221" s="44"/>
+      <c r="E221" s="45"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
-      <c r="B222" s="48"/>
+      <c r="B222" s="40"/>
       <c r="C222" s="5"/>
       <c r="D222" s="6"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="7"/>
-      <c r="B223" s="44"/>
+      <c r="B223" s="41"/>
       <c r="C223" s="8"/>
       <c r="D223" s="9"/>
       <c r="E223" s="8"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="7"/>
-      <c r="B224" s="44"/>
+      <c r="B224" s="41"/>
       <c r="C224" s="8"/>
       <c r="D224" s="9"/>
       <c r="E224" s="8"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="7"/>
-      <c r="B225" s="44"/>
+      <c r="B225" s="41"/>
       <c r="C225" s="8"/>
       <c r="D225" s="9"/>
       <c r="E225" s="8"/>
     </row>
     <row r="226" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="10"/>
-      <c r="B226" s="45"/>
+      <c r="B226" s="42"/>
       <c r="C226" s="10"/>
       <c r="D226" s="11"/>
       <c r="E226" s="10"/>
     </row>
     <row r="227" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B227" s="40"/>
-      <c r="C227" s="41"/>
-      <c r="D227" s="41"/>
-      <c r="E227" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B227" s="43"/>
+      <c r="C227" s="44"/>
+      <c r="D227" s="44"/>
+      <c r="E227" s="45"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="4"/>
-      <c r="B228" s="48"/>
+      <c r="B228" s="40"/>
       <c r="C228" s="5"/>
       <c r="D228" s="6"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="7"/>
-      <c r="B229" s="44"/>
+      <c r="B229" s="41"/>
       <c r="C229" s="8"/>
       <c r="D229" s="9"/>
       <c r="E229" s="8"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="7"/>
-      <c r="B230" s="44"/>
+      <c r="B230" s="41"/>
       <c r="C230" s="8"/>
       <c r="D230" s="9"/>
       <c r="E230" s="8"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="7"/>
-      <c r="B231" s="44"/>
+      <c r="B231" s="41"/>
       <c r="C231" s="8"/>
       <c r="D231" s="9"/>
       <c r="E231" s="8"/>
     </row>
     <row r="232" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
-      <c r="B232" s="45"/>
+      <c r="B232" s="42"/>
       <c r="C232" s="10"/>
       <c r="D232" s="11"/>
       <c r="E232" s="10"/>
     </row>
     <row r="233" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B233" s="40"/>
-      <c r="C233" s="41"/>
-      <c r="D233" s="41"/>
-      <c r="E233" s="42"/>
+        <v>15</v>
+      </c>
+      <c r="B233" s="43"/>
+      <c r="C233" s="44"/>
+      <c r="D233" s="44"/>
+      <c r="E233" s="45"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="13"/>
@@ -2738,7 +2805,7 @@
     </row>
     <row r="239" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B239" s="24"/>
       <c r="C239" s="25"/>
@@ -2747,7 +2814,7 @@
     </row>
     <row r="240" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B240" s="28"/>
       <c r="C240" s="15">
@@ -2758,27 +2825,54 @@
       <c r="E240" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="83">
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E60:E63"/>
-    <mergeCell ref="B156:B160"/>
-    <mergeCell ref="B155:E155"/>
-    <mergeCell ref="B150:B154"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B144:B148"/>
-    <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B174:B178"/>
-    <mergeCell ref="B173:E173"/>
-    <mergeCell ref="B168:B172"/>
-    <mergeCell ref="B161:E161"/>
+  <mergeCells count="78">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B66:B70"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B132:B136"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B120:B124"/>
+    <mergeCell ref="B113:E113"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B102:B106"/>
     <mergeCell ref="B101:E101"/>
     <mergeCell ref="B96:B100"/>
     <mergeCell ref="B233:E233"/>
@@ -2795,53 +2889,21 @@
     <mergeCell ref="B192:B196"/>
     <mergeCell ref="B185:E185"/>
     <mergeCell ref="B180:B184"/>
-    <mergeCell ref="B120:B124"/>
-    <mergeCell ref="B113:E113"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B132:B136"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B84:B88"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:B52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B66:B70"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B174:B178"/>
+    <mergeCell ref="B173:E173"/>
+    <mergeCell ref="B168:B172"/>
+    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B156:B160"/>
+    <mergeCell ref="B155:E155"/>
+    <mergeCell ref="B150:B154"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B144:B148"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E60:E63"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E26:E27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Durée par tranche de 10min" error="Le nombre doit être de type entier" sqref="C48:C52 C42:C46 C234:C238 C36:C40 C18:C22 B6 C12:C16 C228:C232 C60:C64 C6:C10 C24:C28 C30:C34 C54:C58 C72:C76 C66:C70 C84:C88 C78:C82 C96:C100 C90:C94 C114:C118 C108:C112 C126:C130 C120:C124 C138:C142 C132:C136 C150:C154 C144:C148 C162:C166 C156:C160 C174:C178 C168:C172 C186:C190 C180:C184 C198:C202 C192:C196 C210:C214 C204:C208 C222:C226 C216:C220 C102:C106" xr:uid="{345ABA8F-B69F-4AFC-9D0E-D2AB0ACDE277}">
@@ -2851,14 +2913,21 @@
       <formula1>45261</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E7" r:id="rId1" xr:uid="{0F042922-6E00-4A35-A170-701BD284F765}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{21EDFC41-CC09-44F1-8428-4DF1D5596B15}"/>
+    <hyperlink ref="E13" r:id="rId3" xr:uid="{783A9A1F-7763-4F38-B4D8-1507D75E9D73}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{F24EEC4B-090E-442E-86B9-1960A63AC2FF}"/>
+    <hyperlink ref="E14" r:id="rId5" xr:uid="{BC09E3E6-736E-4276-B5DB-2A8D7DDEA696}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId6"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Etml_font,Normal"&amp;22ETML&amp;R&amp;G</oddHeader>
     <oddFooter>&amp;L&amp;14&amp;D&amp;R&amp;14Journal</oddFooter>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
+  <legacyDrawingHF r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -2872,12 +2941,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000A5FF5060FAA704B8B8EC8536792D478" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="1d122ee42f4440bdb76bae0e867ea8cf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00db2195-f9cc-4024-b3af-1f1627d43e67" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0a0e119627867d559f5e44675fb6e73" ns2:_="">
     <xsd:import namespace="00db2195-f9cc-4024-b3af-1f1627d43e67"/>
@@ -3015,6 +3078,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BCAAC0-9C03-42D2-8685-2E30F60CCBAA}">
   <ds:schemaRefs>
@@ -3024,15 +3093,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE5610C-8295-4DF9-896F-27896B117771}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9E7A4E0-CE90-450A-A45E-2949B6138EF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3048,4 +3108,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE5610C-8295-4DF9-896F-27896B117771}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>